--- a/sample-data/facecheck-dhoni-kohli-demo.xlsx
+++ b/sample-data/facecheck-dhoni-kohli-demo.xlsx
@@ -116,7 +116,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/5/5e/MS_Dhoni_2016.jpg</t>
+          <t>https://res.cloudinary.com/ddph6chua/image/upload/f_jpg/v1791716042/Indian-cricketer-Mahendra-Singh-Dhoni-2011.jpg_sp3i9q.webp</t>
         </is>
       </c>
     </row>
@@ -141,7 +141,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/1/15/Virat_Kohli_portrait.jpg</t>
+          <t>https://res.cloudinary.com/ddph6chua/image/upload/v1791716041/images-2_ucp4q0.jpg</t>
         </is>
       </c>
     </row>
